--- a/SGC-CKN/Excel/6434b904-6b71-4b5b-aae6-faa930d3b20c_Lô_CT-02_P1-118_D800_27-03-2026.xlsx
+++ b/SGC-CKN/Excel/6434b904-6b71-4b5b-aae6-faa930d3b20c_Lô_CT-02_P1-118_D800_27-03-2026.xlsx
@@ -106,7 +106,7 @@
 27/03/2026</t>
   </si>
   <si>
-    <t>Độ sâu 0,66 ghi chú là MPDN (Mặt phẳng đất nền)</t>
+    <t>Độ sâu 0,66 ghi chú là M ĐTN</t>
   </si>
   <si>
     <t>2</t>
